--- a/backend/data/financials_by_company/0444.HK.xlsx
+++ b/backend/data/financials_by_company/0444.HK.xlsx
@@ -677,57 +677,59 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45382</v>
+        <v>44651</v>
       </c>
       <c r="B2" t="n">
-        <v>376.577754</v>
+        <v>-1467840</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1e-05</v>
+        <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>-178430000</v>
+        <v>-93908000</v>
       </c>
       <c r="E2" t="n">
-        <v>12292000</v>
+        <v>-8896000</v>
       </c>
       <c r="F2" t="n">
-        <v>12292000</v>
+        <v>-8896000</v>
       </c>
       <c r="G2" t="n">
-        <v>-196896000</v>
+        <v>-156819000</v>
       </c>
       <c r="H2" t="n">
-        <v>6911000</v>
+        <v>30886000</v>
       </c>
       <c r="I2" t="n">
-        <v>144673000</v>
+        <v>91880000</v>
       </c>
       <c r="J2" t="n">
-        <v>-166138000</v>
+        <v>-102804000</v>
       </c>
       <c r="K2" t="n">
-        <v>-173049000</v>
+        <v>-133690000</v>
       </c>
       <c r="L2" t="n">
-        <v>-22264000</v>
+        <v>-20435000</v>
       </c>
       <c r="M2" t="n">
-        <v>22799000</v>
+        <v>21102000</v>
       </c>
       <c r="N2" t="n">
-        <v>535000</v>
+        <v>667000</v>
       </c>
       <c r="O2" t="n">
-        <v>-209187623.422246</v>
+        <v>-149390840</v>
       </c>
       <c r="P2" t="n">
-        <v>-196896000</v>
+        <v>-156819000</v>
       </c>
       <c r="Q2" t="n">
-        <v>268086000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>199472000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>863000</v>
+      </c>
       <c r="S2" t="n">
         <v>6043950000</v>
       </c>
@@ -735,91 +737,97 @@
         <v>6043950000</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0326</v>
+        <v>-0.0259</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0326</v>
+        <v>-0.0259</v>
       </c>
       <c r="W2" t="n">
-        <v>-196896000</v>
+        <v>-156819000</v>
       </c>
       <c r="X2" t="n">
-        <v>-196896000</v>
+        <v>-156819000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-196896000</v>
+        <v>-156819000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1054000</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-195842000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>-156819000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="n">
-        <v>-195842000</v>
+        <v>-156819000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-6000</v>
+        <v>2027000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-195848000</v>
+        <v>-154792000</v>
       </c>
       <c r="AG2" t="n">
-        <v>2626000</v>
+        <v>-234000</v>
       </c>
       <c r="AH2" t="n">
-        <v>12213000</v>
+        <v>-10068000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-23050000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>-1006000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1063000</v>
+      </c>
       <c r="AK2" t="n">
-        <v>10837000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>11074000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
       <c r="AM2" t="n">
-        <v>-22264000</v>
+        <v>-20435000</v>
       </c>
       <c r="AN2" t="n">
-        <v>22799000</v>
+        <v>21102000</v>
       </c>
       <c r="AO2" t="n">
-        <v>535000</v>
+        <v>667000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-142439000</v>
+        <v>-50753000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>123413000</v>
+        <v>107592000</v>
       </c>
       <c r="AR2" t="n">
-        <v>2208000</v>
+        <v>1063000</v>
       </c>
       <c r="AS2" t="n">
-        <v>121205000</v>
+        <v>106723000</v>
       </c>
       <c r="AT2" t="n">
-        <v>15913000</v>
+        <v>34992000</v>
       </c>
       <c r="AU2" t="n">
-        <v>105292000</v>
+        <v>71731000</v>
       </c>
       <c r="AV2" t="n">
-        <v>-19026000</v>
+        <v>56839000</v>
       </c>
       <c r="AW2" t="n">
-        <v>144673000</v>
+        <v>91880000</v>
       </c>
       <c r="AX2" t="n">
-        <v>125647000</v>
+        <v>148719000</v>
       </c>
       <c r="AY2" t="n">
-        <v>125647000</v>
+        <v>148719000</v>
       </c>
     </row>
     <row r="3">
@@ -975,59 +983,57 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
+        <v>45382</v>
       </c>
       <c r="B4" t="n">
-        <v>-1467840</v>
+        <v>376.577754</v>
       </c>
       <c r="C4" t="n">
-        <v>0.165</v>
+        <v>3.1e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>-93908000</v>
+        <v>-178430000</v>
       </c>
       <c r="E4" t="n">
-        <v>-8896000</v>
+        <v>12292000</v>
       </c>
       <c r="F4" t="n">
-        <v>-8896000</v>
+        <v>12292000</v>
       </c>
       <c r="G4" t="n">
-        <v>-156819000</v>
+        <v>-196896000</v>
       </c>
       <c r="H4" t="n">
-        <v>30886000</v>
+        <v>6911000</v>
       </c>
       <c r="I4" t="n">
-        <v>91880000</v>
+        <v>144673000</v>
       </c>
       <c r="J4" t="n">
-        <v>-102804000</v>
+        <v>-166138000</v>
       </c>
       <c r="K4" t="n">
-        <v>-133690000</v>
+        <v>-173049000</v>
       </c>
       <c r="L4" t="n">
-        <v>-20435000</v>
+        <v>-22264000</v>
       </c>
       <c r="M4" t="n">
-        <v>21102000</v>
+        <v>22799000</v>
       </c>
       <c r="N4" t="n">
-        <v>667000</v>
+        <v>535000</v>
       </c>
       <c r="O4" t="n">
-        <v>-149390840</v>
+        <v>-209187623.422246</v>
       </c>
       <c r="P4" t="n">
-        <v>-156819000</v>
+        <v>-196896000</v>
       </c>
       <c r="Q4" t="n">
-        <v>199472000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>863000</v>
-      </c>
+        <v>268086000</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>6043950000</v>
       </c>
@@ -1035,97 +1041,91 @@
         <v>6043950000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0259</v>
+        <v>-0.0326</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0259</v>
+        <v>-0.0326</v>
       </c>
       <c r="W4" t="n">
-        <v>-156819000</v>
+        <v>-196896000</v>
       </c>
       <c r="X4" t="n">
-        <v>-156819000</v>
+        <v>-196896000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-156819000</v>
+        <v>-196896000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-1054000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-156819000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
+        <v>-195842000</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-156819000</v>
+        <v>-195842000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2027000</v>
+        <v>-6000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-154792000</v>
+        <v>-195848000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-234000</v>
+        <v>2626000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-10068000</v>
+        <v>12213000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1006000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1063000</v>
-      </c>
+        <v>-23050000</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>11074000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
+        <v>10837000</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>-20435000</v>
+        <v>-22264000</v>
       </c>
       <c r="AN4" t="n">
-        <v>21102000</v>
+        <v>22799000</v>
       </c>
       <c r="AO4" t="n">
-        <v>667000</v>
+        <v>535000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-50753000</v>
+        <v>-142439000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>107592000</v>
+        <v>123413000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1063000</v>
+        <v>2208000</v>
       </c>
       <c r="AS4" t="n">
-        <v>106723000</v>
+        <v>121205000</v>
       </c>
       <c r="AT4" t="n">
-        <v>34992000</v>
+        <v>15913000</v>
       </c>
       <c r="AU4" t="n">
-        <v>71731000</v>
+        <v>105292000</v>
       </c>
       <c r="AV4" t="n">
-        <v>56839000</v>
+        <v>-19026000</v>
       </c>
       <c r="AW4" t="n">
-        <v>91880000</v>
+        <v>144673000</v>
       </c>
       <c r="AX4" t="n">
-        <v>148719000</v>
+        <v>125647000</v>
       </c>
       <c r="AY4" t="n">
-        <v>148719000</v>
+        <v>125647000</v>
       </c>
     </row>
   </sheetData>
@@ -1446,11 +1446,9 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45382</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
+        <v>44651</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>6043950000</v>
       </c>
@@ -1458,43 +1456,43 @@
         <v>6043950000</v>
       </c>
       <c r="E2" t="n">
-        <v>285409000</v>
+        <v>223934000</v>
       </c>
       <c r="F2" t="n">
-        <v>361002000</v>
+        <v>367226000</v>
       </c>
       <c r="G2" t="n">
-        <v>31920000</v>
+        <v>546879000</v>
       </c>
       <c r="H2" t="n">
-        <v>341449000</v>
+        <v>842012000</v>
       </c>
       <c r="I2" t="n">
-        <v>-184805000</v>
+        <v>264247000</v>
       </c>
       <c r="J2" t="n">
-        <v>31920000</v>
+        <v>546879000</v>
       </c>
       <c r="K2" t="n">
-        <v>51473000</v>
+        <v>72093000</v>
       </c>
       <c r="L2" t="n">
-        <v>31920000</v>
+        <v>546879000</v>
       </c>
       <c r="M2" t="n">
-        <v>232486000</v>
+        <v>804037000</v>
       </c>
       <c r="N2" t="n">
-        <v>32756000</v>
+        <v>546879000</v>
       </c>
       <c r="O2" t="n">
-        <v>836000</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>31920000</v>
+        <v>546879000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-968016000</v>
+        <v>-496620000</v>
       </c>
       <c r="R2" t="n">
         <v>964354000</v>
@@ -1506,127 +1504,125 @@
         <v>120879000</v>
       </c>
       <c r="U2" t="n">
-        <v>523126000</v>
+        <v>471328000</v>
       </c>
       <c r="V2" t="n">
-        <v>232049000</v>
+        <v>301116000</v>
       </c>
       <c r="W2" t="n">
-        <v>232049000</v>
+        <v>301116000</v>
       </c>
       <c r="X2" t="n">
-        <v>31483000</v>
+        <v>43958000</v>
       </c>
       <c r="Y2" t="n">
-        <v>200566000</v>
+        <v>257158000</v>
       </c>
       <c r="Z2" t="n">
-        <v>291077000</v>
+        <v>170212000</v>
       </c>
       <c r="AA2" t="n">
-        <v>128953000</v>
+        <v>66110000</v>
       </c>
       <c r="AB2" t="n">
-        <v>19990000</v>
+        <v>28135000</v>
       </c>
       <c r="AC2" t="n">
-        <v>108963000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>16051000</v>
-      </c>
+        <v>37975000</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>133048000</v>
+        <v>51824000</v>
       </c>
       <c r="AF2" t="n">
-        <v>68950000</v>
+        <v>19106000</v>
       </c>
       <c r="AG2" t="n">
-        <v>44000</v>
+        <v>1579000</v>
       </c>
       <c r="AH2" t="n">
-        <v>64054000</v>
+        <v>31139000</v>
       </c>
       <c r="AI2" t="n">
-        <v>555882000</v>
+        <v>1018207000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>449610000</v>
+        <v>583748000</v>
       </c>
       <c r="AK2" t="n">
-        <v>10432000</v>
+        <v>8217000</v>
       </c>
       <c r="AL2" t="n">
         <v>94000</v>
       </c>
       <c r="AM2" t="n">
-        <v>3234000</v>
+        <v>7894000</v>
       </c>
       <c r="AN2" t="n">
-        <v>3234000</v>
+        <v>7894000</v>
       </c>
       <c r="AO2" t="n">
-        <v>424103000</v>
+        <v>522366000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6533000</v>
+        <v>44437000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-280869000</v>
+        <v>-268299000</v>
       </c>
       <c r="AR2" t="n">
-        <v>287402000</v>
+        <v>312736000</v>
       </c>
       <c r="AS2" t="n">
-        <v>208324000</v>
+        <v>218630000</v>
       </c>
       <c r="AT2" t="n">
-        <v>11589000</v>
+        <v>12223000</v>
       </c>
       <c r="AU2" t="n">
-        <v>67489000</v>
+        <v>81883000</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>106272000</v>
+        <v>434459000</v>
       </c>
       <c r="AX2" t="n">
-        <v>4987000</v>
+        <v>18524000</v>
       </c>
       <c r="AY2" t="n">
-        <v>18367000</v>
+        <v>22504000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>44495000</v>
+        <v>280810000</v>
       </c>
       <c r="BA2" t="n">
-        <v>44495000</v>
+        <v>280810000</v>
       </c>
       <c r="BB2" t="n">
-        <v>10769000</v>
+        <v>20525000</v>
       </c>
       <c r="BC2" t="n">
-        <v>2122000</v>
+        <v>19429000</v>
       </c>
       <c r="BD2" t="n">
-        <v>-3625000</v>
+        <v>-16787000</v>
       </c>
       <c r="BE2" t="n">
-        <v>5747000</v>
+        <v>36216000</v>
       </c>
       <c r="BF2" t="n">
-        <v>25532000</v>
+        <v>72667000</v>
       </c>
       <c r="BG2" t="n">
-        <v>1412000</v>
+        <v>1468000</v>
       </c>
       <c r="BH2" t="n">
-        <v>24120000</v>
+        <v>71199000</v>
       </c>
       <c r="BI2" t="n">
-        <v>24120000</v>
+        <v>71199000</v>
       </c>
     </row>
     <row r="3">
@@ -1814,9 +1810,11 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45382</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
         <v>6043950000</v>
       </c>
@@ -1824,43 +1822,43 @@
         <v>6043950000</v>
       </c>
       <c r="E4" t="n">
-        <v>223934000</v>
+        <v>285409000</v>
       </c>
       <c r="F4" t="n">
-        <v>367226000</v>
+        <v>361002000</v>
       </c>
       <c r="G4" t="n">
-        <v>546879000</v>
+        <v>31920000</v>
       </c>
       <c r="H4" t="n">
-        <v>842012000</v>
+        <v>341449000</v>
       </c>
       <c r="I4" t="n">
-        <v>264247000</v>
+        <v>-184805000</v>
       </c>
       <c r="J4" t="n">
-        <v>546879000</v>
+        <v>31920000</v>
       </c>
       <c r="K4" t="n">
-        <v>72093000</v>
+        <v>51473000</v>
       </c>
       <c r="L4" t="n">
-        <v>546879000</v>
+        <v>31920000</v>
       </c>
       <c r="M4" t="n">
-        <v>804037000</v>
+        <v>232486000</v>
       </c>
       <c r="N4" t="n">
-        <v>546879000</v>
+        <v>32756000</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>836000</v>
       </c>
       <c r="P4" t="n">
-        <v>546879000</v>
+        <v>31920000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-496620000</v>
+        <v>-968016000</v>
       </c>
       <c r="R4" t="n">
         <v>964354000</v>
@@ -1872,125 +1870,127 @@
         <v>120879000</v>
       </c>
       <c r="U4" t="n">
-        <v>471328000</v>
+        <v>523126000</v>
       </c>
       <c r="V4" t="n">
-        <v>301116000</v>
+        <v>232049000</v>
       </c>
       <c r="W4" t="n">
-        <v>301116000</v>
+        <v>232049000</v>
       </c>
       <c r="X4" t="n">
-        <v>43958000</v>
+        <v>31483000</v>
       </c>
       <c r="Y4" t="n">
-        <v>257158000</v>
+        <v>200566000</v>
       </c>
       <c r="Z4" t="n">
-        <v>170212000</v>
+        <v>291077000</v>
       </c>
       <c r="AA4" t="n">
-        <v>66110000</v>
+        <v>128953000</v>
       </c>
       <c r="AB4" t="n">
-        <v>28135000</v>
+        <v>19990000</v>
       </c>
       <c r="AC4" t="n">
-        <v>37975000</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
+        <v>108963000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>16051000</v>
+      </c>
       <c r="AE4" t="n">
-        <v>51824000</v>
+        <v>133048000</v>
       </c>
       <c r="AF4" t="n">
-        <v>19106000</v>
+        <v>68950000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1579000</v>
+        <v>44000</v>
       </c>
       <c r="AH4" t="n">
-        <v>31139000</v>
+        <v>64054000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1018207000</v>
+        <v>555882000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>583748000</v>
+        <v>449610000</v>
       </c>
       <c r="AK4" t="n">
-        <v>8217000</v>
+        <v>10432000</v>
       </c>
       <c r="AL4" t="n">
         <v>94000</v>
       </c>
       <c r="AM4" t="n">
-        <v>7894000</v>
+        <v>3234000</v>
       </c>
       <c r="AN4" t="n">
-        <v>7894000</v>
+        <v>3234000</v>
       </c>
       <c r="AO4" t="n">
-        <v>522366000</v>
+        <v>424103000</v>
       </c>
       <c r="AP4" t="n">
-        <v>44437000</v>
+        <v>6533000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-268299000</v>
+        <v>-280869000</v>
       </c>
       <c r="AR4" t="n">
-        <v>312736000</v>
+        <v>287402000</v>
       </c>
       <c r="AS4" t="n">
-        <v>218630000</v>
+        <v>208324000</v>
       </c>
       <c r="AT4" t="n">
-        <v>12223000</v>
+        <v>11589000</v>
       </c>
       <c r="AU4" t="n">
-        <v>81883000</v>
+        <v>67489000</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>434459000</v>
+        <v>106272000</v>
       </c>
       <c r="AX4" t="n">
-        <v>18524000</v>
+        <v>4987000</v>
       </c>
       <c r="AY4" t="n">
-        <v>22504000</v>
+        <v>18367000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>280810000</v>
+        <v>44495000</v>
       </c>
       <c r="BA4" t="n">
-        <v>280810000</v>
+        <v>44495000</v>
       </c>
       <c r="BB4" t="n">
-        <v>20525000</v>
+        <v>10769000</v>
       </c>
       <c r="BC4" t="n">
-        <v>19429000</v>
+        <v>2122000</v>
       </c>
       <c r="BD4" t="n">
-        <v>-16787000</v>
+        <v>-3625000</v>
       </c>
       <c r="BE4" t="n">
-        <v>36216000</v>
+        <v>5747000</v>
       </c>
       <c r="BF4" t="n">
-        <v>72667000</v>
+        <v>25532000</v>
       </c>
       <c r="BG4" t="n">
-        <v>1468000</v>
+        <v>1412000</v>
       </c>
       <c r="BH4" t="n">
-        <v>71199000</v>
+        <v>24120000</v>
       </c>
       <c r="BI4" t="n">
-        <v>71199000</v>
+        <v>24120000</v>
       </c>
     </row>
   </sheetData>
@@ -2226,124 +2226,126 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45382</v>
+        <v>44651</v>
       </c>
       <c r="B2" t="n">
-        <v>5164000</v>
+        <v>6686000</v>
       </c>
       <c r="C2" t="n">
-        <v>-160932000</v>
+        <v>-92624000</v>
       </c>
       <c r="D2" t="n">
-        <v>184197000</v>
+        <v>114417000</v>
       </c>
       <c r="E2" t="n">
-        <v>-2951000</v>
+        <v>-7903000</v>
       </c>
       <c r="F2" t="n">
-        <v>24120000</v>
+        <v>71199000</v>
       </c>
       <c r="G2" t="n">
-        <v>51434000</v>
+        <v>90802000</v>
       </c>
       <c r="H2" t="n">
-        <v>-9014000</v>
+        <v>-864000</v>
       </c>
       <c r="I2" t="n">
-        <v>-18300000</v>
+        <v>-18739000</v>
       </c>
       <c r="J2" t="n">
-        <v>-17938000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>331000</v>
-      </c>
+        <v>-29977000</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-18082000</v>
+        <v>-19196000</v>
       </c>
       <c r="M2" t="n">
-        <v>23265000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>21793000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>15000000</v>
+      </c>
       <c r="P2" t="n">
-        <v>23265000</v>
+        <v>6793000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-160932000</v>
+        <v>-92624000</v>
       </c>
       <c r="R2" t="n">
-        <v>184197000</v>
+        <v>99417000</v>
       </c>
       <c r="S2" t="n">
-        <v>-8477000</v>
+        <v>-3351000</v>
       </c>
       <c r="T2" t="n">
-        <v>9037000</v>
+        <v>-75000</v>
       </c>
       <c r="U2" t="n">
-        <v>535000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>-11535000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-11535000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+        <v>667000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3960000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3960000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
       <c r="AB2" t="n">
-        <v>-2151000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>800000</v>
-      </c>
+        <v>-7903000</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>-2951000</v>
+        <v>-7903000</v>
       </c>
       <c r="AE2" t="n">
-        <v>8115000</v>
+        <v>14589000</v>
       </c>
       <c r="AF2" t="n">
-        <v>6000</v>
+        <v>-568000</v>
       </c>
       <c r="AG2" t="n">
-        <v>112457000</v>
+        <v>29112000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-132000</v>
+        <v>58000</v>
       </c>
       <c r="AI2" t="n">
-        <v>905000</v>
+        <v>9281000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>108234000</v>
+        <v>23949000</v>
       </c>
       <c r="AK2" t="n">
-        <v>3450000</v>
+        <v>-4176000</v>
       </c>
       <c r="AL2" t="n">
-        <v>14000</v>
+        <v>19429000</v>
       </c>
       <c r="AM2" t="n">
-        <v>6911000</v>
+        <v>30886000</v>
       </c>
       <c r="AN2" t="n">
-        <v>6911000</v>
+        <v>30886000</v>
       </c>
       <c r="AO2" t="n">
-        <v>35332000</v>
+        <v>73558000</v>
       </c>
       <c r="AP2" t="n">
-        <v>9877000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-800000</v>
-      </c>
+        <v>270000</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>-195848000</v>
+        <v>-154792000</v>
       </c>
     </row>
     <row r="3">
@@ -2478,126 +2480,124 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
+        <v>45382</v>
       </c>
       <c r="B4" t="n">
-        <v>6686000</v>
+        <v>5164000</v>
       </c>
       <c r="C4" t="n">
-        <v>-92624000</v>
+        <v>-160932000</v>
       </c>
       <c r="D4" t="n">
-        <v>114417000</v>
+        <v>184197000</v>
       </c>
       <c r="E4" t="n">
-        <v>-7903000</v>
+        <v>-2951000</v>
       </c>
       <c r="F4" t="n">
-        <v>71199000</v>
+        <v>24120000</v>
       </c>
       <c r="G4" t="n">
-        <v>90802000</v>
+        <v>51434000</v>
       </c>
       <c r="H4" t="n">
-        <v>-864000</v>
+        <v>-9014000</v>
       </c>
       <c r="I4" t="n">
-        <v>-18739000</v>
+        <v>-18300000</v>
       </c>
       <c r="J4" t="n">
-        <v>-29977000</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
+        <v>-17938000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>331000</v>
+      </c>
       <c r="L4" t="n">
-        <v>-19196000</v>
+        <v>-18082000</v>
       </c>
       <c r="M4" t="n">
-        <v>21793000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>15000000</v>
-      </c>
+        <v>23265000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>6793000</v>
+        <v>23265000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-92624000</v>
+        <v>-160932000</v>
       </c>
       <c r="R4" t="n">
-        <v>99417000</v>
+        <v>184197000</v>
       </c>
       <c r="S4" t="n">
-        <v>-3351000</v>
+        <v>-8477000</v>
       </c>
       <c r="T4" t="n">
-        <v>-75000</v>
+        <v>9037000</v>
       </c>
       <c r="U4" t="n">
-        <v>667000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>3960000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3960000</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
+        <v>535000</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>-11535000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-11535000</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>-7903000</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>-2151000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>800000</v>
+      </c>
       <c r="AD4" t="n">
-        <v>-7903000</v>
+        <v>-2951000</v>
       </c>
       <c r="AE4" t="n">
-        <v>14589000</v>
+        <v>8115000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-568000</v>
+        <v>6000</v>
       </c>
       <c r="AG4" t="n">
-        <v>29112000</v>
+        <v>112457000</v>
       </c>
       <c r="AH4" t="n">
-        <v>58000</v>
+        <v>-132000</v>
       </c>
       <c r="AI4" t="n">
-        <v>9281000</v>
+        <v>905000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23949000</v>
+        <v>108234000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-4176000</v>
+        <v>3450000</v>
       </c>
       <c r="AL4" t="n">
-        <v>19429000</v>
+        <v>14000</v>
       </c>
       <c r="AM4" t="n">
-        <v>30886000</v>
+        <v>6911000</v>
       </c>
       <c r="AN4" t="n">
-        <v>30886000</v>
+        <v>6911000</v>
       </c>
       <c r="AO4" t="n">
-        <v>73558000</v>
+        <v>35332000</v>
       </c>
       <c r="AP4" t="n">
-        <v>270000</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
+        <v>9877000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-800000</v>
+      </c>
       <c r="AR4" t="n">
-        <v>-154792000</v>
+        <v>-195848000</v>
       </c>
     </row>
   </sheetData>
@@ -3127,192 +3127,192 @@
       </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
         </is>
       </c>
       <c r="EK1" t="inlineStr">
@@ -3572,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BU2" t="n">
         <v>0.0016</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>Sincere Watch (Hong Kong) Limited</t>
+          <t>PREPRE</t>
         </is>
       </c>
       <c r="CZ2" t="b">
@@ -3729,69 +3729,71 @@
       <c r="DK2" t="n">
         <v>0</v>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DL2" t="n">
+        <v>1750935540</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>1751284800</v>
+      </c>
+      <c r="DN2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>SINCEREWATCH HK</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>Sincere Watch (Hong Kong) Limited</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DM2" t="n">
+      <c r="DS2" t="n">
         <v>1750902228</v>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DV2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>finmb_24193306</t>
         </is>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DR2" t="n">
+      <c r="DZ2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DS2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1750935540</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1751284800</v>
-      </c>
-      <c r="DZ2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="EB2" t="n">
+      <c r="EB2" t="b">
         <v>0</v>
       </c>
       <c r="EC2" t="n">
@@ -3804,21 +3806,19 @@
         <v>0</v>
       </c>
       <c r="EF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
         <v>-1.4285713</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>15</v>
       </c>
       <c r="EH2" t="n">
         <v>15</v>
       </c>
-      <c r="EI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>SINCEREWATCH HK</t>
-        </is>
+      <c r="EI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EJ2" t="b">
+        <v>0</v>
       </c>
       <c r="EK2" t="inlineStr"/>
     </row>
